--- a/docs/build/lakeshore-enterprise-context/source/07_data_analytics_reporting/kpi_definitions.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/07_data_analytics_reporting/kpi_definitions.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Conflicting</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -576,12 +576,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Conflicting</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -630,12 +630,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Certified</t>
+          <t>Draft</t>
         </is>
       </c>
     </row>
@@ -657,12 +657,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Certified</t>
         </is>
       </c>
     </row>
@@ -684,12 +684,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Maria Donnelly</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Certified</t>
+          <t>Conflicting</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Conflicting</t>
         </is>
       </c>
     </row>
